--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,173 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F8" s="3">
         <v>32600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>24100</v>
       </c>
-      <c r="F8" s="3">
-        <v>58800</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>31900</v>
+      </c>
+      <c r="I8" s="3">
         <v>21800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>19000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>47200</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F9" s="3">
         <v>26000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>19600</v>
       </c>
-      <c r="F9" s="3">
-        <v>48900</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>26800</v>
+      </c>
+      <c r="I9" s="3">
         <v>18800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>16000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>39900</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F10" s="3">
         <v>6600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4500</v>
       </c>
-      <c r="F10" s="3">
-        <v>9900</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I10" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>7300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +861,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +898,14 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +939,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +980,14 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1021,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1039,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>43800</v>
+      </c>
+      <c r="F17" s="3">
         <v>32100</v>
       </c>
-      <c r="E17" s="3">
-        <v>27600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>60500</v>
-      </c>
       <c r="G17" s="3">
+        <v>26800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>31600</v>
+      </c>
+      <c r="I17" s="3">
         <v>23700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>19900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>45400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1700</v>
-      </c>
       <c r="G18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,78 +1138,92 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-400</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1400</v>
+        <v>-3600</v>
       </c>
       <c r="E21" s="3">
-        <v>-2100</v>
+        <v>-800</v>
       </c>
       <c r="F21" s="3">
-        <v>-1300</v>
+        <v>200</v>
       </c>
       <c r="G21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1900</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1169,87 +1248,105 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>800</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1380,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E26" s="3">
-        <v>-3100</v>
+        <v>-1400</v>
       </c>
       <c r="F26" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E27" s="3">
-        <v>-3100</v>
+        <v>-1400</v>
       </c>
       <c r="F27" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1503,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1544,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1585,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1626,96 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>400</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E33" s="3">
-        <v>-3100</v>
+        <v>-1400</v>
       </c>
       <c r="F33" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1749,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E35" s="3">
-        <v>-3100</v>
+        <v>-1400</v>
       </c>
       <c r="F35" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1857,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,26 +1874,28 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>25700</v>
+      </c>
+      <c r="F41" s="3">
         <v>40300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>24000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>84300</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,23 +1911,29 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F42" s="3">
         <v>9100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9600</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,32 +1946,38 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F43" s="3">
         <v>24500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>15400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>18000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,8 +1993,14 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1817,17 +2008,17 @@
         <v>7500</v>
       </c>
       <c r="E44" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G44" s="3">
         <v>14200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>20300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1843,26 +2034,32 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
         <v>3400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,26 +2075,32 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>81600</v>
+      </c>
+      <c r="F46" s="3">
         <v>84800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>63600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>122800</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,8 +2116,14 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1948,26 +2157,32 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1983,26 +2198,32 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>700</v>
       </c>
       <c r="E49" s="3">
-        <v>72700</v>
-      </c>
-      <c r="F49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
         <v>73500</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,8 +2239,14 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2280,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,8 +2321,14 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2102,11 +2341,11 @@
       <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>700</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2123,8 +2362,14 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,26 +2403,32 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>88400</v>
+      </c>
+      <c r="F54" s="3">
         <v>90700</v>
       </c>
-      <c r="E54" s="3">
-        <v>142000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>69200</v>
+      </c>
+      <c r="H54" s="3">
         <v>201100</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,8 +2444,14 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2465,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,26 +2482,28 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>50700</v>
+      </c>
+      <c r="F57" s="3">
         <v>53000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>56200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>67700</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,8 +2519,14 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2293,26 +2560,32 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>47300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,26 +2601,32 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>54000</v>
+      </c>
+      <c r="F60" s="3">
         <v>56000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>58400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>115000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2642,14 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2398,26 +2683,32 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2724,14 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2765,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2806,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,26 +2847,32 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>57400</v>
+      </c>
+      <c r="F66" s="3">
         <v>59300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>62000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>117800</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2888,14 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2909,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2946,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2987,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3028,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,26 +3069,32 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F72" s="3">
         <v>5800</v>
       </c>
-      <c r="E72" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H72" s="3">
         <v>9000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +3110,14 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3151,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3192,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,26 +3233,32 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F76" s="3">
         <v>31400</v>
       </c>
-      <c r="E76" s="3">
-        <v>80000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H76" s="3">
         <v>83200</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +3274,14 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3315,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E81" s="3">
-        <v>-3100</v>
+        <v>-1400</v>
       </c>
       <c r="F81" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,34 +3423,36 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>-800</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3063,8 +3460,14 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3501,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3542,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3583,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3624,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3665,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-9800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6600</v>
       </c>
-      <c r="F89" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>16400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-15700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-8300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,16 +3727,18 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-500</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
@@ -3306,14 +3747,14 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -3323,8 +3764,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3805,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,34 +3846,40 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
@@ -3428,8 +3887,14 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3908,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3945,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3986,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4027,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +4068,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F100" s="3">
         <v>26200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-44000</v>
       </c>
-      <c r="F100" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,39 +4150,51 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="F102" s="3">
         <v>16300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-60200</v>
       </c>
-      <c r="F102" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3">
         <v>14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,64 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,38 +724,41 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E8" s="3">
         <v>41700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>42900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32600</v>
       </c>
-      <c r="G8" s="3">
-        <v>24100</v>
-      </c>
       <c r="H8" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I8" s="3">
         <v>31900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -764,38 +768,41 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E9" s="3">
         <v>35300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26000</v>
       </c>
-      <c r="G9" s="3">
-        <v>19600</v>
-      </c>
       <c r="H9" s="3">
+        <v>68700</v>
+      </c>
+      <c r="I9" s="3">
         <v>26800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,38 +812,41 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E10" s="3">
         <v>6400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6600</v>
       </c>
-      <c r="G10" s="3">
-        <v>4500</v>
-      </c>
       <c r="H10" s="3">
+        <v>14300</v>
+      </c>
+      <c r="I10" s="3">
         <v>5100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3000</v>
       </c>
       <c r="J10" s="3">
         <v>3000</v>
       </c>
       <c r="K10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L10" s="3">
         <v>7300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -846,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +962,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,8 +1006,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -997,20 +1020,20 @@
       <c r="E15" s="3">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,38 +1067,39 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E17" s="3">
         <v>45600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32100</v>
       </c>
-      <c r="G17" s="3">
-        <v>26800</v>
-      </c>
       <c r="H17" s="3">
+        <v>86600</v>
+      </c>
+      <c r="I17" s="3">
         <v>31600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,38 +1109,41 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1123,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,38 +1173,39 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,38 +1215,41 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="H21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1259,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1254,47 +1294,50 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,38 +1347,41 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1345,8 +1391,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,38 +1435,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,38 +1479,41 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,8 +1523,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,38 +1699,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,38 +1743,41 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1787,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,38 +1831,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1796,43 +1875,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1924,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,29 +1962,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E41" s="3">
         <v>17500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,26 +2004,29 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>9300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9600</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1952,35 +2042,38 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E43" s="3">
         <v>45600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,29 +2092,32 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,29 +2136,32 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,29 +2180,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E46" s="3">
         <v>83000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>81600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>84800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>63600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>122800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,31 +2224,34 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2163,29 +2268,32 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E48" s="3">
         <v>6100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,29 +2312,32 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="3">
         <v>700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3">
         <v>73500</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,8 +2444,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2347,8 +2467,8 @@
       <c r="H52" s="3">
         <v>700</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>700</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2368,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,29 +2532,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E54" s="3">
         <v>90600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>201100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,29 +2614,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E57" s="3">
         <v>55000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,8 +2656,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2566,29 +2700,32 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,29 +2744,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E60" s="3">
         <v>58500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>115000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,8 +2788,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2689,29 +2832,32 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3400</v>
       </c>
       <c r="F62" s="3">
         <v>3400</v>
       </c>
       <c r="G62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,29 +3008,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E66" s="3">
         <v>61600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>117800</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,29 +3246,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E72" s="3">
         <v>500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,29 +3422,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E76" s="3">
         <v>29000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>83200</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3280,8 +3466,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,43 +3510,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3367,38 +3559,41 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3408,8 +3603,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,13 +3623,14 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -3440,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3454,8 +3653,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,38 +3885,41 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9800</v>
       </c>
-      <c r="G89" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="H89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>16400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3929,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,35 +3949,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,37 +4079,40 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="H94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3893,8 +4123,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,38 +4317,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
-        <v>26200</v>
-      </c>
       <c r="G100" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+        <v>25500</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4115,8 +4361,11 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4156,38 +4405,41 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-60200</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="H102" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>14100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4195,6 +4447,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,211 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>37300</v>
+      </c>
+      <c r="F8" s="3">
         <v>30000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>41700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>42900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>32600</v>
       </c>
-      <c r="H8" s="3">
-        <v>83000</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>24100</v>
+      </c>
+      <c r="K8" s="3">
         <v>31900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>21800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>19000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>47200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F9" s="3">
         <v>23900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>35300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>36000</v>
       </c>
-      <c r="G9" s="3">
-        <v>26000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>68700</v>
-      </c>
       <c r="I9" s="3">
+        <v>26100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>19600</v>
+      </c>
+      <c r="K9" s="3">
         <v>26800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>18800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>16000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>39900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F10" s="3">
         <v>6100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6400</v>
       </c>
-      <c r="F10" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6600</v>
-      </c>
       <c r="H10" s="3">
-        <v>14300</v>
+        <v>6800</v>
       </c>
       <c r="I10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K10" s="3">
         <v>5100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,31 +903,33 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>300</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="I12" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -921,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,31 +999,37 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1009,37 +1049,43 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1053,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>40700</v>
+      </c>
+      <c r="F17" s="3">
         <v>35700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>45600</v>
       </c>
-      <c r="F17" s="3">
-        <v>43800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>32100</v>
-      </c>
       <c r="H17" s="3">
-        <v>86600</v>
+        <v>43700</v>
       </c>
       <c r="I17" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K17" s="3">
         <v>31600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>23700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>45400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
-        <v>500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3600</v>
-      </c>
       <c r="I18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,119 +1240,133 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5600</v>
+        <v>-4900</v>
       </c>
       <c r="E21" s="3">
-        <v>-3600</v>
+        <v>-3000</v>
       </c>
       <c r="F21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
-        <v>200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1297,105 +1377,123 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>100</v>
-      </c>
       <c r="H23" s="3">
-        <v>-3400</v>
+        <v>-800</v>
       </c>
       <c r="I23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
-        <v>-4500</v>
+        <v>-1300</v>
       </c>
       <c r="I26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
-        <v>-4500</v>
+        <v>-1300</v>
       </c>
       <c r="I27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
-        <v>-4500</v>
+        <v>-1300</v>
       </c>
       <c r="I33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
-        <v>-4500</v>
+        <v>-1300</v>
       </c>
       <c r="I35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,35 +2135,37 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F41" s="3">
         <v>39500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>25700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>40300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>24000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>84300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,8 +2181,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2016,23 +2196,23 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>9300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>9200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>9100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,41 +2225,47 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>47900</v>
+        <v>62400</v>
       </c>
       <c r="E43" s="3">
-        <v>45600</v>
+        <v>60200</v>
       </c>
       <c r="F43" s="3">
+        <v>48100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>45700</v>
+      </c>
+      <c r="H43" s="3">
         <v>39400</v>
       </c>
-      <c r="G43" s="3">
-        <v>24500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J43" s="3">
         <v>15400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>18000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,35 +2281,41 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9800</v>
+        <v>7000</v>
       </c>
       <c r="E44" s="3">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F44" s="3">
-        <v>5600</v>
+        <v>10000</v>
       </c>
       <c r="G44" s="3">
-        <v>7500</v>
+        <v>8700</v>
       </c>
       <c r="H44" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J44" s="3">
         <v>14200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>20300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2139,35 +2331,41 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3400</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>300</v>
-      </c>
-      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,35 +2381,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>102600</v>
+      </c>
+      <c r="F46" s="3">
         <v>98700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>83000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>81600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>84800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>63600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>122800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,20 +2431,26 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F47" s="3">
         <v>2000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,11 +2463,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2271,35 +2481,41 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F48" s="3">
         <v>5800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5900</v>
       </c>
-      <c r="G48" s="3">
-        <v>5100</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J48" s="3">
         <v>4900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,35 +2531,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>73500</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2581,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,16 +2681,22 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>700</v>
@@ -2468,13 +2708,13 @@
         <v>700</v>
       </c>
       <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>700</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2491,8 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,35 +2781,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>122600</v>
+      </c>
+      <c r="F54" s="3">
         <v>108100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>90600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>88400</v>
       </c>
-      <c r="G54" s="3">
-        <v>90700</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>90400</v>
+      </c>
+      <c r="J54" s="3">
         <v>69200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>201100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2831,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,35 +2875,37 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>70800</v>
+      </c>
+      <c r="F57" s="3">
         <v>64700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>55000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>50700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>53000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>56200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>67700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,31 +2921,37 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2703,35 +2971,41 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5000</v>
+        <v>13500</v>
       </c>
       <c r="E59" s="3">
-        <v>3600</v>
+        <v>12500</v>
       </c>
       <c r="F59" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G59" s="3">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="H59" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>900</v>
+      </c>
+      <c r="K59" s="3">
         <v>47300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,35 +3021,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>86000</v>
+      </c>
+      <c r="F60" s="3">
         <v>69700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>58500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>54000</v>
       </c>
-      <c r="G60" s="3">
-        <v>56000</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>55900</v>
+      </c>
+      <c r="J60" s="3">
         <v>58400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>115000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,31 +3071,37 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2835,35 +3121,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3171,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,35 +3321,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>88200</v>
+      </c>
+      <c r="F66" s="3">
         <v>72500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>61600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>57400</v>
       </c>
-      <c r="G66" s="3">
-        <v>59300</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>58900</v>
+      </c>
+      <c r="J66" s="3">
         <v>62000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>117800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3371,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,35 +3591,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>500</v>
       </c>
-      <c r="F72" s="3">
-        <v>5100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>5800</v>
-      </c>
       <c r="H72" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I72" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J72" s="3">
         <v>7400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3641,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,35 +3791,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F76" s="3">
         <v>35700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>29000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>31000</v>
       </c>
-      <c r="G76" s="3">
-        <v>31400</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>31500</v>
+      </c>
+      <c r="J76" s="3">
         <v>7200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>83200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3841,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
-        <v>-4500</v>
+        <v>-1300</v>
       </c>
       <c r="I81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,43 +4020,45 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3668,8 +4066,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F89" s="3">
         <v>3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-9800</v>
-      </c>
       <c r="H89" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>-13100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-10100</v>
       </c>
       <c r="J89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>16400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-15700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3959,16 +4401,16 @@
         <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="F91" s="3">
-        <v>-800</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-500</v>
@@ -3977,14 +4419,14 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -3994,8 +4436,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,43 +4536,49 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F94" s="3">
         <v>7800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4126,8 +4586,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,31 +4610,33 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4188,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,75 +4806,87 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>25500</v>
-      </c>
       <c r="H100" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+        <v>-700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>26400</v>
       </c>
       <c r="J100" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4408,48 +4906,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F102" s="3">
         <v>22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-14600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>16300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-50400</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3">
+        <v>-60200</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>14100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-14100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,76 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,47 +735,50 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E8" s="3">
         <v>39300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>31900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>47200</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -785,47 +788,50 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E9" s="3">
         <v>31700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23900</v>
       </c>
-      <c r="G9" s="3">
-        <v>35300</v>
-      </c>
       <c r="H9" s="3">
+        <v>35400</v>
+      </c>
+      <c r="I9" s="3">
         <v>36000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,8 +841,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,38 +853,38 @@
         <v>7700</v>
       </c>
       <c r="E10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F10" s="3">
         <v>10600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6100</v>
       </c>
-      <c r="G10" s="3">
-        <v>6400</v>
-      </c>
       <c r="H10" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I10" s="3">
         <v>6800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>3000</v>
       </c>
       <c r="M10" s="3">
         <v>3000</v>
       </c>
       <c r="N10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O10" s="3">
         <v>7300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,34 +917,35 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>-800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
-        <v>300</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>-100</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+      <c r="K12" s="3">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
@@ -955,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1031,8 +1050,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1055,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1064,14 +1086,14 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1081,14 +1103,14 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1105,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,47 +1147,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E17" s="3">
         <v>44600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>43700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45400</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1172,47 +1198,50 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-900</v>
+        <v>-3900</v>
       </c>
       <c r="I18" s="3">
         <v>-900</v>
       </c>
       <c r="J18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,47 +1274,48 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,47 +1325,50 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1356,8 +1395,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1368,8 +1407,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1383,56 +1422,59 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-3700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1442,8 +1484,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1451,38 +1496,38 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
       </c>
       <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1492,8 +1537,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,47 +1590,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1592,47 +1643,50 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1642,8 +1696,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,47 +1908,50 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1892,47 +1961,50 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1942,8 +2014,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,47 +2067,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,52 +2120,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2097,8 +2178,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,38 +2222,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E41" s="3">
         <v>37700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2202,20 +2291,20 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>9300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9600</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2231,44 +2320,47 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E43" s="3">
         <v>62400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2287,38 +2379,41 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E44" s="3">
         <v>7000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,8 +2432,11 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2354,21 +2452,21 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,38 +2485,41 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E46" s="3">
         <v>108500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>102600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>98700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>81600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>84800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>63600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,23 +2538,26 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12200</v>
+        <v>12100</v>
       </c>
       <c r="E47" s="3">
         <v>12200</v>
       </c>
       <c r="F47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G47" s="3">
         <v>2000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2573,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2487,38 +2591,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,38 +2644,41 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>300</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>73500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,8 +2697,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,19 +2803,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
@@ -2708,16 +2827,16 @@
         <v>700</v>
       </c>
       <c r="I52" s="3">
+        <v>700</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>700</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2737,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,38 +2909,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E54" s="3">
         <v>129000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>90600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>201100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,38 +3006,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E57" s="3">
         <v>80300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>70800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>64700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3057,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2939,23 +3072,23 @@
         <v>1200</v>
       </c>
       <c r="F58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1200</v>
       </c>
       <c r="H58" s="3">
         <v>1200</v>
       </c>
       <c r="I58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2977,38 +3110,41 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="3">
         <v>13500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2100</v>
       </c>
       <c r="H59" s="3">
         <v>2100</v>
       </c>
       <c r="I59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,38 +3163,41 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E60" s="3">
         <v>96400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>115000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,35 +3216,38 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3127,8 +3269,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3153,12 +3298,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,38 +3481,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107800</v>
+      </c>
+      <c r="E66" s="3">
         <v>98200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>117800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,38 +3767,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,38 +3979,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E76" s="3">
         <v>30700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>34500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,52 +4085,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3952,47 +4143,50 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4196,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4031,28 +4229,28 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>-200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4060,8 +4258,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4072,8 +4270,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,47 +4535,50 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3400</v>
       </c>
-      <c r="G89" s="3">
-        <v>-7400</v>
-      </c>
       <c r="H89" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-13100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>16400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4372,8 +4588,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,44 +4611,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-500</v>
       </c>
       <c r="I91" s="3">
         <v>-500</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4442,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,46 +4768,49 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4592,8 +4821,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4635,12 +4868,12 @@
       <c r="I96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>3400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,47 +5054,50 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>10800</v>
       </c>
-      <c r="G100" s="3">
-        <v>200</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4862,8 +5107,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4888,8 +5136,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4912,47 +5160,50 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E102" s="3">
         <v>2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-60200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>14100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4960,6 +5211,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,50 +739,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E8" s="3">
         <v>41800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>39300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>31900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,50 +795,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E9" s="3">
         <v>34100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39900</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,50 +851,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>7700</v>
+        <v>4800</v>
       </c>
       <c r="E10" s="3">
         <v>7700</v>
       </c>
       <c r="F10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="G10" s="3">
         <v>10600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5100</v>
-      </c>
-      <c r="M10" s="3">
-        <v>3000</v>
       </c>
       <c r="N10" s="3">
         <v>3000</v>
       </c>
       <c r="O10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P10" s="3">
         <v>7300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +931,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,26 +943,26 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>-800</v>
       </c>
-      <c r="G12" s="3">
-        <v>200</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>-100</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
+      <c r="L12" s="3">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1041,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,8 +1073,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1077,8 +1097,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1089,14 +1112,14 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
@@ -1106,14 +1129,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,50 +1174,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E17" s="3">
         <v>49200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>45400</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,50 +1228,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-900</v>
       </c>
       <c r="J18" s="3">
         <v>-900</v>
       </c>
       <c r="K18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1284,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,50 +1308,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1328,50 +1362,53 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-5700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,13 +1418,16 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1410,8 +1450,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1425,59 +1465,62 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1487,50 +1530,53 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>500</v>
       </c>
       <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,50 +1642,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,50 +1698,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1754,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,50 +1978,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,50 +2034,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2090,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,50 +2146,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,55 +2202,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2263,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2309,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E41" s="3">
         <v>34400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2363,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2294,20 +2384,20 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>9300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,47 +2413,50 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E43" s="3">
         <v>67700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>60200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,41 +2475,44 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>20300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2531,11 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2455,21 +2554,21 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,41 +2587,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E46" s="3">
         <v>112300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>83000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>84800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>122800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,26 +2643,29 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E47" s="3">
         <v>12100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>12200</v>
       </c>
       <c r="F47" s="3">
         <v>12200</v>
       </c>
       <c r="G47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2576,8 +2681,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2594,41 +2699,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2656,32 +2767,32 @@
         <v>2100</v>
       </c>
       <c r="E49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1400</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>300</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>73500</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2815,13 +2935,13 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
@@ -2830,16 +2950,16 @@
         <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>700</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>700</v>
       </c>
       <c r="L52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>700</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3035,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E54" s="3">
         <v>132000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>129000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>90600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>88400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>201100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3091,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,41 +3137,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E57" s="3">
         <v>91500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>80300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>50700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>53000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,13 +3191,16 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
         <v>1200</v>
@@ -3075,23 +3209,23 @@
         <v>1200</v>
       </c>
       <c r="G58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H58" s="3">
         <v>1300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1200</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3113,41 +3247,44 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2100</v>
       </c>
       <c r="I59" s="3">
         <v>2100</v>
       </c>
       <c r="J59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,41 +3303,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E60" s="3">
         <v>106200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>69700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>58500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>115000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,38 +3359,41 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3272,8 +3415,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3301,12 +3447,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3639,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E66" s="3">
         <v>107800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>88200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>117800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3695,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3941,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-22400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3997,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4165,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E76" s="3">
         <v>24200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>83200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4221,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,55 +4277,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,50 +4338,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,8 +4394,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,40 +4418,41 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>-200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4261,8 +4460,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,50 +4752,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>16400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4808,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,47 +4832,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
       </c>
       <c r="J91" s="3">
         <v>-500</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,49 +4998,52 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4824,8 +5054,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4871,12 +5105,12 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>3400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,50 +5300,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>2300</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>10800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-43900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5356,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5139,8 +5388,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5163,50 +5412,53 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-60200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>14100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5214,6 +5466,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,91 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,59 +750,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E8" s="3">
         <v>30400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>39300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>37300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>47200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -812,59 +815,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E9" s="3">
         <v>25200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,59 +880,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E10" s="3">
         <v>5100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>7700</v>
       </c>
       <c r="H10" s="3">
         <v>7700</v>
       </c>
       <c r="I10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J10" s="3">
         <v>10600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3000</v>
       </c>
       <c r="Q10" s="3">
         <v>3000</v>
       </c>
       <c r="R10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S10" s="3">
         <v>7300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,46 +972,47 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>-100</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>0</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -1022,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1122,8 +1141,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1146,19 +1165,22 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1167,14 +1189,14 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1184,14 +1206,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1208,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,59 +1254,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E17" s="3">
         <v>33000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>49200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>45400</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,59 +1317,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-900</v>
       </c>
       <c r="M18" s="3">
         <v>-900</v>
       </c>
       <c r="N18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,13 +1409,14 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1392,44 +1425,44 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,59 +1472,62 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1501,28 +1537,31 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1539,8 +1578,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1554,68 +1593,71 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1625,59 +1667,62 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>500</v>
       </c>
       <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1687,8 +1732,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,59 +1797,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1811,59 +1862,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1873,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,13 +2187,16 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -2136,44 +2205,44 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,59 +2252,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,59 +2382,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2369,64 +2447,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2436,8 +2517,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E41" s="3">
         <v>22700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2573,20 +2662,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>9300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9600</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2602,56 +2691,59 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E43" s="3">
         <v>45200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>60400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>45700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,50 +2762,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6900</v>
-      </c>
-      <c r="E44" s="3">
-        <v>7800</v>
       </c>
       <c r="F44" s="3">
         <v>7800</v>
       </c>
       <c r="G44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H44" s="3">
         <v>7900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>20300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2732,8 +2827,11 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2761,21 +2859,21 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E46" s="3">
         <v>75100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>72900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>94000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>112300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>102600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>83000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>84800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>63600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>122800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,35 +2957,38 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E47" s="3">
         <v>11300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>12200</v>
       </c>
       <c r="I47" s="3">
         <v>12200</v>
       </c>
       <c r="J47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K47" s="3">
         <v>2000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2900,8 +3004,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2918,50 +3022,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,50 +3087,53 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2200</v>
-      </c>
-      <c r="F49" s="3">
-        <v>2100</v>
       </c>
       <c r="G49" s="3">
         <v>2100</v>
       </c>
       <c r="H49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I49" s="3">
         <v>2000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>300</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>73500</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3175,22 +3294,22 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>7600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
@@ -3199,16 +3318,16 @@
         <v>700</v>
       </c>
       <c r="M52" s="3">
+        <v>700</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>700</v>
       </c>
       <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>700</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3228,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E54" s="3">
         <v>96400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>115700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>132000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>129000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>90600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>88400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>90400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>201100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E57" s="3">
         <v>52100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>81800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>91500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>80300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>70800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>64700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>53000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>67700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,22 +3592,25 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1200</v>
       </c>
       <c r="H58" s="3">
         <v>1200</v>
@@ -3486,23 +3619,23 @@
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1200</v>
       </c>
       <c r="L58" s="3">
         <v>1200</v>
       </c>
       <c r="M58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3524,50 +3657,53 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E59" s="3">
         <v>9800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2100</v>
       </c>
       <c r="L59" s="3">
         <v>2100</v>
       </c>
       <c r="M59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>47300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E60" s="3">
         <v>65800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>86000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>54000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>58400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>115000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,47 +3787,50 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3710,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3719,11 +3864,11 @@
         <v>29000</v>
       </c>
       <c r="E62" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F62" s="3">
         <v>25000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3748,12 +3893,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E66" s="3">
         <v>98200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>101600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>107800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>88200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>117800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-14400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>83200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,64 +4852,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4731,59 +4922,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4793,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,40 +5024,40 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
+        <v>500</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
       </c>
       <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>-200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4867,8 +5065,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4879,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,59 +5402,62 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>16400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5251,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,56 +5494,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-500</v>
       </c>
       <c r="M91" s="3">
         <v>-500</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5337,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,58 +5687,61 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5523,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5582,12 +5815,12 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3">
         <v>3400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,59 +6037,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>10800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>26400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5857,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5895,8 +6143,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5919,59 +6167,62 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-60200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>14100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5979,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>ISPR</t>
   </si>
@@ -656,94 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,62 +754,65 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E8" s="3">
         <v>20300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>37300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>47200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,62 +822,65 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E9" s="3">
         <v>16800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>34100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,62 +890,65 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>7700</v>
       </c>
       <c r="I10" s="3">
         <v>7700</v>
       </c>
       <c r="J10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K10" s="3">
         <v>10600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>3000</v>
       </c>
       <c r="R10" s="3">
         <v>3000</v>
       </c>
       <c r="S10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T10" s="3">
         <v>7300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +986,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,38 +998,38 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
         <v>-100</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -1038,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1120,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1144,8 +1164,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1177,13 +1200,13 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1192,14 +1215,14 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1209,14 +1232,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,62 +1281,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E17" s="3">
         <v>27200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>49200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>45400</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,62 +1347,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-900</v>
       </c>
       <c r="N18" s="3">
         <v>-900</v>
       </c>
       <c r="O18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1415,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,16 +1443,17 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1428,44 +1462,44 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1475,62 +1509,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1577,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1551,11 +1591,11 @@
       <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1563,8 +1603,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1581,8 +1621,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1596,71 +1636,74 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,62 +1713,65 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
       </c>
       <c r="I24" s="3">
         <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,62 +1849,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,62 +1917,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1985,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,16 +2257,19 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2208,44 +2278,44 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,62 +2325,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2393,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,62 +2461,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,67 +2529,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2520,8 +2602,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,53 +2656,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E41" s="3">
         <v>17600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2722,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2665,20 +2755,20 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>9300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,59 +2784,62 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E43" s="3">
         <v>38400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>67700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>62400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>60200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,53 +2858,56 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E44" s="3">
         <v>6000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>7800</v>
       </c>
       <c r="G44" s="3">
         <v>7800</v>
       </c>
       <c r="H44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I44" s="3">
         <v>7900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>20300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2830,13 +2926,16 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2862,21 +2961,21 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,53 +2994,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E46" s="3">
         <v>63700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>75100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>94000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>112300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>102600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>98700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>83000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>84800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>63600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>122800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,38 +3062,41 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E47" s="3">
         <v>11100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>12200</v>
       </c>
       <c r="J47" s="3">
         <v>12200</v>
       </c>
       <c r="K47" s="3">
+        <v>12200</v>
+      </c>
+      <c r="L47" s="3">
         <v>2000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3007,8 +3112,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3025,53 +3130,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,53 +3198,56 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2100</v>
       </c>
       <c r="H49" s="3">
         <v>2100</v>
       </c>
       <c r="I49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J49" s="3">
         <v>2000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1400</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>300</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>73500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3402,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3297,22 +3417,22 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>7600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>700</v>
@@ -3321,16 +3441,16 @@
         <v>700</v>
       </c>
       <c r="N52" s="3">
+        <v>700</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>700</v>
       </c>
       <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>700</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,53 +3538,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E54" s="3">
         <v>84400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>96400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>132000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>129000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>122600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>90600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>88400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>90400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>201100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,53 +3660,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E57" s="3">
         <v>45600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>81800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>91500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>80300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>70800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>55000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>50700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>56200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>67700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,25 +3726,28 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1200</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
@@ -3622,23 +3756,23 @@
         <v>1200</v>
       </c>
       <c r="K58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L58" s="3">
         <v>1300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1200</v>
       </c>
       <c r="M58" s="3">
         <v>1200</v>
       </c>
       <c r="N58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3660,53 +3794,56 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2100</v>
       </c>
       <c r="M59" s="3">
         <v>2100</v>
       </c>
       <c r="N59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,53 +3862,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E60" s="3">
         <v>60200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>72500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>106200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>69700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>54000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>58400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>115000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,50 +3930,53 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3855,23 +3998,26 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29000</v>
+        <v>35000</v>
       </c>
       <c r="E62" s="3">
         <v>29000</v>
       </c>
       <c r="F62" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G62" s="3">
         <v>25000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3896,12 +4042,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,8 +4270,11 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4124,44 +4282,44 @@
         <v>92100</v>
       </c>
       <c r="E66" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F66" s="3">
         <v>98200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>101600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>107800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>88200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>117800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,53 +4636,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-57900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-51300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,53 +4908,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-7700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>31500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>83200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,67 +5044,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4925,62 +5117,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4990,8 +5185,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5213,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5027,40 +5226,40 @@
         <v>500</v>
       </c>
       <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
       </c>
       <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>-200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -5068,8 +5267,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5080,8 +5279,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,62 +5619,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>16400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5687,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,59 +5715,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-500</v>
       </c>
       <c r="N91" s="3">
         <v>-500</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5560,8 +5781,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,61 +5917,64 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5755,8 +5985,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5818,12 +6052,12 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3">
         <v>3400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,62 +6283,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>10800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>26400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-43900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-2300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6351,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6146,8 +6395,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6170,62 +6419,65 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-60200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>14100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6485,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
